--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1299,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103699430</v>
+        <v>120493452</v>
       </c>
       <c r="B7" t="n">
-        <v>89175</v>
+        <v>97908</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,38 +1311,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2015</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Blajkvät, SO om Hejde, Gtl</t>
+          <t>Bruten, Bruten, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701008.3558778027</v>
+        <v>700548</v>
       </c>
       <c r="R7" t="n">
-        <v>6366918.387734691</v>
+        <v>6366234</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1369,22 +1369,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,26 +1389,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103703850</v>
+        <v>120493232</v>
       </c>
       <c r="B8" t="n">
-        <v>96355</v>
+        <v>103452</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,54 +1413,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>220164</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blajkvät, SO om Hejde, Gtl</t>
+          <t>Bruten, Bruten, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701004.818400054</v>
+        <v>700582</v>
       </c>
       <c r="R8" t="n">
-        <v>6366913.356230651</v>
+        <v>6366394</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,27 +1471,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 vinterståndare.</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,38 +1485,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre, senvuxen kalktallskog.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103703879</v>
+        <v>120493421</v>
       </c>
       <c r="B9" t="n">
-        <v>85105</v>
+        <v>106214</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1570,49 +1515,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3712</v>
+        <v>221849</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blajkvät, SO om Hejde, Gtl</t>
+          <t>Bruten, Bruten, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700968.7803666922</v>
+        <v>700541</v>
       </c>
       <c r="R9" t="n">
-        <v>6366876.501010303</v>
+        <v>6366241</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,27 +1573,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1 ex. under senvuxen gran.</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1668,31 +1587,1357 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre, senvuxen kalktallskog.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120507149</v>
+      </c>
+      <c r="B10" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>700619</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6366361</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gran, en, tall, Intill grandinge</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120506912</v>
+      </c>
+      <c r="B11" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Klinte, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>700628</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6366355</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Flera små fruktkroppar inne i en liten grandunge</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120507146</v>
+      </c>
+      <c r="B12" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>700621</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6366367</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120493244</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97908</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bruten, Bruten, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>700590</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6366381</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120507144</v>
+      </c>
+      <c r="B14" t="n">
+        <v>86396</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>473</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Äggspindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius meinhardii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Bon</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>700623</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6366369</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120493229</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106214</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bruten, Bruten, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>700582</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6366393</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>103699430</v>
+      </c>
+      <c r="B16" t="n">
+        <v>89175</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Blajkvät, SO om Hejde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>701008.3558778027</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6366918.387734691</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>103703850</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96355</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Blajkvät, SO om Hejde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>701004.818400054</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6366913.356230651</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1 vinterståndare.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Äldre, senvuxen kalktallskog.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Gillis Aronsson</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Gillis Aronsson</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AY17" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>103703879</v>
+      </c>
+      <c r="B18" t="n">
+        <v>85105</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Blajkvät, SO om Hejde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>700968.7803666922</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6366876.501010303</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1 ex. under senvuxen gran.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre, senvuxen kalktallskog.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120492759</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97908</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Utskogen, Utskogen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>700973</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6366729</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120492803</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Utskogen, Utskogen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>701020</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6366713</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120492809</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97908</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Utskogen, Utskogen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>701013</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6366707</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -1817,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120507146</v>
+        <v>120493244</v>
       </c>
       <c r="B12" t="n">
-        <v>86449</v>
+        <v>97908</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,38 +1829,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Bruten, Bruten, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700621</v>
+        <v>700590</v>
       </c>
       <c r="R12" t="n">
-        <v>6366367</v>
+        <v>6366381</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,26 +1907,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120493244</v>
+        <v>120507146</v>
       </c>
       <c r="B13" t="n">
-        <v>97908</v>
+        <v>86449</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,38 +1931,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>6003295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bruten, Bruten, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700590</v>
+        <v>700621</v>
       </c>
       <c r="R13" t="n">
-        <v>6366381</v>
+        <v>6366367</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,15 +2009,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Annica Beil</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -1299,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120493452</v>
+        <v>120493232</v>
       </c>
       <c r="B7" t="n">
-        <v>97908</v>
+        <v>103452</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,25 +1311,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>220164</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700548</v>
+        <v>700582</v>
       </c>
       <c r="R7" t="n">
-        <v>6366234</v>
+        <v>6366394</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120493232</v>
+        <v>120493421</v>
       </c>
       <c r="B8" t="n">
-        <v>103452</v>
+        <v>106214</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,21 +1417,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700582</v>
+        <v>700541</v>
       </c>
       <c r="R8" t="n">
-        <v>6366394</v>
+        <v>6366241</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1503,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120493421</v>
+        <v>120507144</v>
       </c>
       <c r="B9" t="n">
-        <v>106214</v>
+        <v>86396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,34 +1519,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221849</v>
+        <v>473</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bruten, Bruten, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700541</v>
+        <v>700623</v>
       </c>
       <c r="R9" t="n">
-        <v>6366241</v>
+        <v>6366369</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,22 +1593,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Annica Beil</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120507149</v>
+        <v>120506912</v>
       </c>
       <c r="B10" t="n">
-        <v>86282</v>
+        <v>86373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,38 +1621,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3712</v>
+        <v>248956</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Klinte, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700619</v>
+        <v>700628</v>
       </c>
       <c r="R10" t="n">
-        <v>6366361</v>
+        <v>6366355</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,7 +1689,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gran, en, tall, Intill grandinge</t>
+          <t>Flera små fruktkroppar inne i en liten grandunge</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,12 +1704,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Anna Träff</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Anna Träff</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1716,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120506912</v>
+        <v>120507146</v>
       </c>
       <c r="B11" t="n">
-        <v>86373</v>
+        <v>86449</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,38 +1732,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Klinte, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700628</v>
+        <v>700621</v>
       </c>
       <c r="R11" t="n">
-        <v>6366355</v>
+        <v>6366367</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,11 +1798,6 @@
           <t>2024-10-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Flera små fruktkroppar inne i en liten grandunge</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1809,6 +1808,16 @@
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>Naturhänsyns Gotlandsträff 2024</t>
@@ -1817,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120493244</v>
+        <v>120493229</v>
       </c>
       <c r="B12" t="n">
-        <v>97908</v>
+        <v>106214</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,25 +1838,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1857,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700590</v>
+        <v>700582</v>
       </c>
       <c r="R12" t="n">
-        <v>6366381</v>
+        <v>6366393</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1919,10 +1928,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120507146</v>
+        <v>120507149</v>
       </c>
       <c r="B13" t="n">
-        <v>86449</v>
+        <v>86282</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1931,25 +1940,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1959,10 +1968,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700621</v>
+        <v>700619</v>
       </c>
       <c r="R13" t="n">
-        <v>6366367</v>
+        <v>6366361</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,6 +2004,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gran, en, tall, Intill grandinge</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2025,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120507144</v>
+        <v>120493244</v>
       </c>
       <c r="B14" t="n">
-        <v>86396</v>
+        <v>97908</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2037,38 +2051,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>473</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Bruten, Bruten, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700623</v>
+        <v>700590</v>
       </c>
       <c r="R14" t="n">
-        <v>6366369</v>
+        <v>6366381</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2115,26 +2129,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120493229</v>
+        <v>120493452</v>
       </c>
       <c r="B15" t="n">
-        <v>106214</v>
+        <v>97908</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,25 +2153,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700582</v>
+        <v>700548</v>
       </c>
       <c r="R15" t="n">
-        <v>6366393</v>
+        <v>6366234</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2630,7 +2640,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120492759</v>
+        <v>120492809</v>
       </c>
       <c r="B19" t="n">
         <v>97908</v>
@@ -2670,10 +2680,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700973</v>
+        <v>701013</v>
       </c>
       <c r="R19" t="n">
-        <v>6366729</v>
+        <v>6366707</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2732,10 +2742,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120492803</v>
+        <v>120492759</v>
       </c>
       <c r="B20" t="n">
-        <v>57336</v>
+        <v>97908</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2744,43 +2754,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Utskogen, Utskogen, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701020</v>
+        <v>700973</v>
       </c>
       <c r="R20" t="n">
-        <v>6366713</v>
+        <v>6366729</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2839,10 +2844,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120492809</v>
+        <v>120492803</v>
       </c>
       <c r="B21" t="n">
-        <v>97908</v>
+        <v>57336</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2851,38 +2856,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Utskogen, Utskogen, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>701013</v>
+        <v>701020</v>
       </c>
       <c r="R21" t="n">
-        <v>6366707</v>
+        <v>6366713</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -1299,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120493232</v>
+        <v>120507144</v>
       </c>
       <c r="B7" t="n">
-        <v>103452</v>
+        <v>86396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,34 +1315,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220164</v>
+        <v>473</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bruten, Bruten, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700582</v>
+        <v>700623</v>
       </c>
       <c r="R7" t="n">
-        <v>6366394</v>
+        <v>6366369</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1389,19 +1389,23 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Annica Beil</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120493421</v>
+        <v>120493229</v>
       </c>
       <c r="B8" t="n">
         <v>106214</v>
@@ -1441,10 +1445,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700541</v>
+        <v>700582</v>
       </c>
       <c r="R8" t="n">
-        <v>6366241</v>
+        <v>6366393</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1503,10 +1507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120507144</v>
+        <v>120493232</v>
       </c>
       <c r="B9" t="n">
-        <v>86396</v>
+        <v>103452</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,34 +1523,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>473</v>
+        <v>220164</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Bruten, Bruten, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700623</v>
+        <v>700582</v>
       </c>
       <c r="R9" t="n">
-        <v>6366369</v>
+        <v>6366394</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,26 +1597,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120506912</v>
+        <v>120507146</v>
       </c>
       <c r="B10" t="n">
-        <v>86373</v>
+        <v>86449</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,38 +1621,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Klinte, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700628</v>
+        <v>700621</v>
       </c>
       <c r="R10" t="n">
-        <v>6366355</v>
+        <v>6366367</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,11 +1687,6 @@
           <t>2024-10-19</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Flera små fruktkroppar inne i en liten grandunge</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1704,12 +1699,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna Träff</t>
+          <t>Annica Beil</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna Träff</t>
+          <t>Annica Beil</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1720,10 +1715,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120507146</v>
+        <v>120506912</v>
       </c>
       <c r="B11" t="n">
-        <v>86449</v>
+        <v>86373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,38 +1727,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Klinte, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700621</v>
+        <v>700628</v>
       </c>
       <c r="R11" t="n">
-        <v>6366367</v>
+        <v>6366355</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,6 +1793,11 @@
           <t>2024-10-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Flera små fruktkroppar inne i en liten grandunge</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1810,12 +1810,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Anna Träff</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Anna Träff</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1826,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120493229</v>
+        <v>120507149</v>
       </c>
       <c r="B12" t="n">
-        <v>106214</v>
+        <v>86282</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,38 +1838,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221849</v>
+        <v>3712</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bruten, Bruten, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700582</v>
+        <v>700619</v>
       </c>
       <c r="R12" t="n">
-        <v>6366393</v>
+        <v>6366361</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,6 +1904,11 @@
           <t>2024-10-19</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gran, en, tall, Intill grandinge</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1916,22 +1921,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Annica Beil</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120507149</v>
+        <v>120493452</v>
       </c>
       <c r="B13" t="n">
-        <v>86282</v>
+        <v>97908</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,34 +1953,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3712</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Bruten, Bruten, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700619</v>
+        <v>700548</v>
       </c>
       <c r="R13" t="n">
-        <v>6366361</v>
+        <v>6366234</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2006,11 +2015,6 @@
           <t>2024-10-19</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gran, en, tall, Intill grandinge</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2023,19 +2027,15 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2141,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120493452</v>
+        <v>120493421</v>
       </c>
       <c r="B15" t="n">
-        <v>97908</v>
+        <v>106214</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2153,25 +2153,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700548</v>
+        <v>700541</v>
       </c>
       <c r="R15" t="n">
-        <v>6366234</v>
+        <v>6366241</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120492809</v>
+        <v>120492759</v>
       </c>
       <c r="B19" t="n">
         <v>97908</v>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701013</v>
+        <v>700973</v>
       </c>
       <c r="R19" t="n">
-        <v>6366707</v>
+        <v>6366729</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120492759</v>
+        <v>120492809</v>
       </c>
       <c r="B20" t="n">
         <v>97908</v>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700973</v>
+        <v>701013</v>
       </c>
       <c r="R20" t="n">
-        <v>6366729</v>
+        <v>6366707</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2949,6 +2949,117 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125769803</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Utskogen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>701037</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6366934</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -2954,7 +2954,7 @@
         <v>125769803</v>
       </c>
       <c r="B22" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -2954,7 +2954,7 @@
         <v>125769803</v>
       </c>
       <c r="B22" t="n">
-        <v>98359</v>
+        <v>98362</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -2954,7 +2954,7 @@
         <v>125769803</v>
       </c>
       <c r="B22" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -2954,7 +2954,7 @@
         <v>125769803</v>
       </c>
       <c r="B22" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -2954,7 +2954,7 @@
         <v>125769803</v>
       </c>
       <c r="B22" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -2954,7 +2954,7 @@
         <v>125769803</v>
       </c>
       <c r="B22" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -2954,7 +2954,7 @@
         <v>125769803</v>
       </c>
       <c r="B22" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -2954,7 +2954,7 @@
         <v>125769803</v>
       </c>
       <c r="B22" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -2954,7 +2954,7 @@
         <v>125769803</v>
       </c>
       <c r="B22" t="n">
-        <v>98377</v>
+        <v>98380</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88788764</v>
+        <v>103703875</v>
       </c>
       <c r="B2" t="n">
-        <v>42760</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101242</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,28 +708,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>9. N Gajstmyrvägen, Gtl</t>
+          <t>Blajkvät, SO om Hejde, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700787.8513138321</v>
+        <v>700999</v>
       </c>
       <c r="R2" t="n">
-        <v>6366542.143489269</v>
+        <v>6366974</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,22 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-06-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-06-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1 ex. under senvuxen gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,34 +774,34 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Äldre, senvuxen kalktallskog.</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103733447</v>
+        <v>120507144</v>
       </c>
       <c r="B3" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,34 +809,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220079</v>
+        <v>473</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väntinge, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700494.0905675289</v>
+        <v>700623</v>
       </c>
       <c r="R3" t="n">
-        <v>6366136.91301894</v>
+        <v>6366369</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,22 +863,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,66 +883,61 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Annica Beil</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Annica Beil</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103733446</v>
+        <v>105052427</v>
       </c>
       <c r="B4" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220079</v>
+        <v>1282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Källnate</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Potamogeton coloratus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Hornem.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väntinge, Gtl</t>
+          <t>Skogs 3:1 400 m S, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700544.7436348954</v>
+        <v>700655</v>
       </c>
       <c r="R4" t="n">
-        <v>6366239.801168716</v>
+        <v>6366408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,22 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1989-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-12-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,70 +980,70 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Brya i gräsmyr</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson, Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+          <t>Projekt Gotlands Flora</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103733452</v>
+        <v>103699430</v>
       </c>
       <c r="B5" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>2015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väntinge, Gtl</t>
+          <t>Blajkvät, SO om Hejde, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700587.3978701761</v>
+        <v>701009</v>
       </c>
       <c r="R5" t="n">
-        <v>6366274.283456657</v>
+        <v>6366918</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,22 +1070,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,15 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103703852</v>
+        <v>103733452</v>
       </c>
       <c r="B6" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,43 +1117,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blajkvät, SO om Hejde, Gtl</t>
+          <t>Väntinge, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700895.2277432252</v>
+        <v>700587</v>
       </c>
       <c r="R6" t="n">
-        <v>6366843.735938367</v>
+        <v>6366274</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,27 +1171,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gamla gnagspår på tallåga, omkr ca. 100 cm.</t>
+          <t>2022-09-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,34 +1185,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Äldre, senvuxen kalktallskog.</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1299,15 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120507146</v>
+        <v>103703879</v>
       </c>
       <c r="B7" t="n">
-        <v>86255</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,34 +1218,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Blajkvät, SO om Hejde, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700621</v>
+        <v>700969</v>
       </c>
       <c r="R7" t="n">
-        <v>6366367</v>
+        <v>6366877</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1369,12 +1283,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 ex. under senvuxen gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,37 +1302,38 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre, senvuxen kalktallskog.</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120507144</v>
+        <v>120507149</v>
       </c>
       <c r="B8" t="n">
-        <v>86201</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,21 +1341,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>473</v>
+        <v>3712</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1445,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700623</v>
+        <v>700619</v>
       </c>
       <c r="R8" t="n">
-        <v>6366369</v>
+        <v>6366361</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,6 +1401,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gran, en, tall, Intill grandinge</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,15 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120493244</v>
+        <v>120492803</v>
       </c>
       <c r="B9" t="n">
-        <v>98028</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,34 +1447,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bruten, Bruten, Gtl</t>
+          <t>Utskogen, Utskogen, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700590</v>
+        <v>701020</v>
       </c>
       <c r="R9" t="n">
-        <v>6366381</v>
+        <v>6366713</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1613,53 +1538,65 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120493452</v>
+        <v>79993659</v>
       </c>
       <c r="B10" t="n">
-        <v>98028</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bruten, Bruten, Gtl</t>
+          <t>9. N. Gajsmyrvägen, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700548</v>
+        <v>700816</v>
       </c>
       <c r="R10" t="n">
-        <v>6366234</v>
+        <v>6366283</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1683,12 +1620,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2019-06-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2019-06-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,71 +1634,84 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120507149</v>
+        <v>88788743</v>
       </c>
       <c r="B11" t="n">
-        <v>86084</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3712</v>
+        <v>101242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>9. N Gajstmyrvägen, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700619</v>
+        <v>700803</v>
       </c>
       <c r="R11" t="n">
-        <v>6366361</v>
+        <v>6366415</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1785,17 +1735,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gran, en, tall, Intill grandinge</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,75 +1749,84 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
+          <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120506912</v>
+        <v>88788764</v>
       </c>
       <c r="B12" t="n">
-        <v>86178</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>248956</v>
+        <v>101242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Klinte, Gtl</t>
+          <t>9. N Gajstmyrvägen, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700628</v>
+        <v>700788</v>
       </c>
       <c r="R12" t="n">
-        <v>6366355</v>
+        <v>6366542</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1896,17 +1850,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Flera små fruktkroppar inne i en liten grandunge</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,37 +1864,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna Träff</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna Träff</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
+          <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120493421</v>
+        <v>95566037</v>
       </c>
       <c r="B13" t="n">
-        <v>106337</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,34 +1898,47 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bruten, Bruten, Gtl</t>
+          <t>9. N. Gajstmyrvägen, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700541</v>
+        <v>700813</v>
       </c>
       <c r="R13" t="n">
-        <v>6366241</v>
+        <v>6366294</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,12 +1965,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2021-06-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2021-06-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2021,33 +1979,33 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120493229</v>
+        <v>111748925</v>
       </c>
       <c r="B14" t="n">
-        <v>106337</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2055,37 +2013,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bruten, Bruten, Gtl</t>
+          <t>9. N Gajstmyrvägen, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700582</v>
+        <v>700818</v>
       </c>
       <c r="R14" t="n">
-        <v>6366393</v>
+        <v>6366402</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2109,12 +2080,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2023-06-24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2023-06-24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,33 +2094,33 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120493232</v>
+        <v>119204541</v>
       </c>
       <c r="B15" t="n">
-        <v>103575</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2157,37 +2128,50 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220164</v>
+        <v>101242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bruten, Bruten, Gtl</t>
+          <t>9. N Gajstmyrvägen, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700582</v>
+        <v>700804</v>
       </c>
       <c r="R15" t="n">
-        <v>6366394</v>
+        <v>6366412</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2211,12 +2195,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,68 +2209,77 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103699430</v>
+        <v>103703852</v>
       </c>
       <c r="B16" t="n">
-        <v>89175</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2015</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Blajkvät, SO om Hejde, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>701008.3558778027</v>
+        <v>700895</v>
       </c>
       <c r="R16" t="n">
-        <v>6366918.387734691</v>
+        <v>6366844</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2316,19 +2309,14 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gamla gnagspår på tallåga, omkr ca. 100 cm.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,18 +2325,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Äldre, senvuxen kalktallskog.</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2359,15 +2363,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103703850</v>
+        <v>103703846</v>
       </c>
       <c r="B17" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2375,38 +2374,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2415,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701004.818400054</v>
+        <v>700996</v>
       </c>
       <c r="R17" t="n">
-        <v>6366913.356230651</v>
+        <v>6366972</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,24 +2435,9 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1 vinterståndare.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2502,15 +2474,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103703879</v>
+        <v>120492759</v>
       </c>
       <c r="B18" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2518,45 +2485,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3712</v>
+        <v>219798</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Blajkvät, SO om Hejde, Gtl</t>
+          <t>Utskogen, Utskogen, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700968.7803666922</v>
+        <v>700973</v>
       </c>
       <c r="R18" t="n">
-        <v>6366876.501010303</v>
+        <v>6366729</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2583,27 +2539,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>1 ex. under senvuxen gran.</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,43 +2553,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Äldre, senvuxen kalktallskog.</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>120492809</v>
       </c>
       <c r="B19" t="n">
-        <v>98028</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2742,55 +2668,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120492803</v>
+        <v>120493244</v>
       </c>
       <c r="B20" t="n">
-        <v>57364</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Utskogen, Utskogen, Gtl</t>
+          <t>Bruten, Bruten, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>701020</v>
+        <v>700590</v>
       </c>
       <c r="R20" t="n">
-        <v>6366713</v>
+        <v>6366381</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2849,15 +2765,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120492759</v>
+        <v>120493304</v>
       </c>
       <c r="B21" t="n">
-        <v>98028</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,14 +2796,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Utskogen, Utskogen, Gtl</t>
+          <t>Bruten, Bruten, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700973</v>
+        <v>700590</v>
       </c>
       <c r="R21" t="n">
-        <v>6366729</v>
+        <v>6366339</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2951,10 +2862,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125769803</v>
+        <v>120493452</v>
       </c>
       <c r="B22" t="n">
-        <v>98380</v>
+        <v>99096</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,41 +2873,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219864</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Utskogen, Gtl</t>
+          <t>Bruten, Bruten, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>701037</v>
+        <v>700548</v>
       </c>
       <c r="R22" t="n">
-        <v>6366934</v>
+        <v>6366234</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3020,22 +2927,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3050,15 +2947,1156 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>103703850</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Blajkvät, SO om Hejde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>701005</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6366913</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1 vinterståndare.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Äldre, senvuxen kalktallskog.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125769803</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99147</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Utskogen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>701037</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6366934</v>
+      </c>
+      <c r="S24" t="n">
+        <v>8</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Karin Berg Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Karin Berg Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>103733446</v>
+      </c>
+      <c r="B25" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>700544</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6366239</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2022-09-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2022-09-24</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>103733447</v>
+      </c>
+      <c r="B26" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Väntinge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>700494</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6366137</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-09-24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-09-24</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120493232</v>
+      </c>
+      <c r="B27" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bruten, Bruten, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>700582</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6366394</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120493229</v>
+      </c>
+      <c r="B28" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bruten, Bruten, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>700582</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6366393</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120493421</v>
+      </c>
+      <c r="B29" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bruten, Bruten, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>700541</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6366241</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120506912</v>
+      </c>
+      <c r="B30" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Klinte, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>700628</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6366355</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Flera små fruktkroppar inne i en liten grandunge</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anna Träff</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anna Träff</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120507147</v>
+      </c>
+      <c r="B31" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>700694</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6366357</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120507148</v>
+      </c>
+      <c r="B32" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>700662</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6366303</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120507146</v>
+      </c>
+      <c r="B33" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>700621</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6366367</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103703875</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507144</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105052427</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103699430</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103733452</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103703879</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1433,6 +1468,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507149</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120492803</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1654,6 +1699,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79993659</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1769,6 +1819,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88788743</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1884,6 +1939,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88788764</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1999,6 +2059,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95566037</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2114,6 +2179,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111748925</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2227,6 +2297,11 @@
       <c r="AY15" t="inlineStr">
         <is>
           <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119204541</t>
         </is>
       </c>
     </row>
@@ -2358,6 +2433,11 @@
       <c r="AY16" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103703852</t>
         </is>
       </c>
     </row>
@@ -2471,6 +2551,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103703846</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2568,6 +2653,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120492759</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2665,6 +2755,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120492809</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2762,6 +2857,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120493244</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2859,6 +2959,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120493304</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2956,6 +3061,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120493452</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3082,6 +3192,11 @@
       <c r="AY23" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103703850</t>
         </is>
       </c>
     </row>
@@ -3195,6 +3310,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125769803</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3296,6 +3416,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103733446</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3397,6 +3522,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103733447</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3494,6 +3624,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120493232</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3591,6 +3726,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120493229</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3688,6 +3828,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120493421</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3794,6 +3939,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120506912</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3895,6 +4045,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507147</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3996,6 +4151,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507148</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4097,8 +4257,47 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507146</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>